--- a/tests/data_golden/expansion.template.xlsx
+++ b/tests/data_golden/expansion.template.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="122">
   <si>
     <t>#{r}${items#r.name}</t>
   </si>
